--- a/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>ERNXY</t>
   </si>
@@ -656,56 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -733,8 +736,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -762,8 +768,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -791,8 +800,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -804,8 +816,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -833,8 +846,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -862,8 +878,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -891,8 +910,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -920,8 +942,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -930,8 +955,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -959,8 +985,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -988,8 +1017,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1001,8 +1033,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1030,8 +1063,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1059,8 +1095,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1088,8 +1127,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1117,8 +1159,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1146,8 +1191,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1175,8 +1223,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1204,8 +1255,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1233,8 +1287,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1262,8 +1319,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1291,8 +1351,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1320,8 +1383,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1349,8 +1415,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1378,8 +1447,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1407,8 +1479,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1436,8 +1511,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1465,42 +1543,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1512,8 +1596,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1525,95 +1610,105 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1732600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1818300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1474400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1736500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1601400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1414600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1305500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1451200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1069900</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E42" s="3">
         <v>68700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>94900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>113400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>113900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>180600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>80900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>114300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>173900</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>439300</v>
+      </c>
+      <c r="E43" s="3">
         <v>510600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>331600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>453700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>400200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>377200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>395400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>505000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>398700</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1641,153 +1736,171 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>207656500</v>
+      </c>
+      <c r="E45" s="3">
         <v>277991200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>222368700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>228851800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>203067600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>194326200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>207307300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>193317000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>178307700</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>209894400</v>
+      </c>
+      <c r="E46" s="3">
         <v>280388800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>224318400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>231155400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>205216400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>196298600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>209128800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>195387500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>179979700</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>370400</v>
+      </c>
+      <c r="E47" s="3">
         <v>301000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>292500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>284700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>295600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>279400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>327200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>384400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>169500</v>
+      </c>
+      <c r="E48" s="3">
         <v>172000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>170600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>176200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>188000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>175000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>181900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>180600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6311400</v>
+      </c>
+      <c r="E49" s="3">
         <v>6790400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6540800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6548500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6751600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6481600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6668300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6671000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6632300</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1815,8 +1928,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1844,37 +1960,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E52" s="3">
         <v>5200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1902,37 +2024,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>216780800</v>
+      </c>
+      <c r="E54" s="3">
         <v>287703500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>231372700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>238204400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>212487400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>203275300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>216338800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>202661200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>187172500</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1944,8 +2072,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1957,182 +2086,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>480700</v>
+      </c>
+      <c r="E57" s="3">
         <v>494600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>310900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>396200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>165200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>366300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>415400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>548800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>173600</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>551100</v>
+      </c>
+      <c r="E58" s="3">
         <v>586900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>556100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>51100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>43600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>34200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>29500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>56000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>207911600</v>
+      </c>
+      <c r="E59" s="3">
         <v>278347100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>222721600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>229240000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>203391900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>194637600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>207548400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>193600000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>178437800</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>208943400</v>
+      </c>
+      <c r="E60" s="3">
         <v>279428600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>223588600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>229687300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>203892000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>195038100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>207993300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>194204700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>178909000</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2674400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2870400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2758800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3312500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3392200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3249200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3353100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3330400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3258300</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E62" s="3">
         <v>9800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2160,8 +2308,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2189,8 +2340,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2218,37 +2372,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>212223400</v>
+      </c>
+      <c r="E66" s="3">
         <v>282963300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>226984600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>233660400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>207971700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>198946500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>212026400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>198213600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>182854500</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2260,8 +2420,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2289,8 +2450,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2318,8 +2482,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2347,8 +2514,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2376,37 +2546,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>1642600</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>1706000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>1355500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>1352700</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2434,8 +2610,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2463,8 +2642,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2492,37 +2674,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4395100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4574500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4244300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4384600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4361300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4186200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4172000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4305600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4182900</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2550,42 +2738,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2613,8 +2807,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2626,37 +2823,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E83" s="3">
         <v>44300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>41200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>44000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-9100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>38000</v>
       </c>
       <c r="I83" s="3">
         <v>38000</v>
       </c>
       <c r="J83" s="3">
+        <v>38000</v>
+      </c>
+      <c r="K83" s="3">
         <v>44700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2684,8 +2885,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2713,8 +2917,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2742,8 +2949,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2771,8 +2981,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2800,37 +3013,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>181200</v>
+      </c>
+      <c r="E89" s="3">
         <v>264800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>119500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>199200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>214900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>184700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>151700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>345700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-157200</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2842,37 +3061,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5300</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3">
         <v>-13300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2900,8 +3123,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2929,37 +3155,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E94" s="3">
         <v>36000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-32100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>71500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>36200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>24000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>37600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-63900</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2971,37 +3203,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
         <v>275700</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>258900</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3029,8 +3265,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3058,8 +3297,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3087,91 +3329,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-108200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-342400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-162000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-79900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-320700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>7900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-15400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-16300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-23000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>11800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E102" s="3">
         <v>283500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-250200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>173400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>124100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>148900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-152800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>363600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-228600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>ERNXY</t>
   </si>
@@ -656,59 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,8 +742,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -771,8 +777,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -803,8 +812,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -817,8 +829,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -849,8 +862,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -881,8 +897,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -913,8 +932,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -945,8 +967,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -956,8 +981,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -988,8 +1014,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1020,8 +1049,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1034,8 +1066,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1066,8 +1099,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1098,8 +1134,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,8 +1169,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1162,8 +1204,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1194,8 +1239,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1226,8 +1274,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1258,8 +1309,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1290,8 +1344,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1322,8 +1379,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1354,8 +1414,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1386,8 +1449,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1418,8 +1484,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1450,8 +1519,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1482,8 +1554,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1514,8 +1589,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1546,45 +1624,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1597,8 +1681,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1611,104 +1696,114 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1732600</v>
+        <v>1775100</v>
       </c>
       <c r="E41" s="3">
+        <v>1732500</v>
+      </c>
+      <c r="F41" s="3">
         <v>1818300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1474400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1736500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1601400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1414600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1305500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1451200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1069900</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>66100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>68700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>94900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>113400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>113900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>180600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>80900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>114300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>173900</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>439300</v>
+        <v>639500</v>
       </c>
       <c r="E43" s="3">
+        <v>406300</v>
+      </c>
+      <c r="F43" s="3">
         <v>510600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>331600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>453700</v>
       </c>
-      <c r="H43" s="3">
-        <v>400200</v>
-      </c>
       <c r="I43" s="3">
+        <v>352600</v>
+      </c>
+      <c r="J43" s="3">
         <v>377200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>395400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>505000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>398700</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1739,168 +1834,186 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>207656500</v>
+        <v>369335600</v>
       </c>
       <c r="E45" s="3">
+        <v>279831000</v>
+      </c>
+      <c r="F45" s="3">
         <v>277991200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>222368700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>228851800</v>
       </c>
-      <c r="H45" s="3">
-        <v>203067600</v>
-      </c>
       <c r="I45" s="3">
+        <v>200097400</v>
+      </c>
+      <c r="J45" s="3">
         <v>194326200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>207307300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>193317000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>178307700</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>209894400</v>
+        <v>371750200</v>
       </c>
       <c r="E46" s="3">
+        <v>282068800</v>
+      </c>
+      <c r="F46" s="3">
         <v>280388800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>224318400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>231155400</v>
       </c>
-      <c r="H46" s="3">
-        <v>205216400</v>
-      </c>
       <c r="I46" s="3">
+        <v>202198600</v>
+      </c>
+      <c r="J46" s="3">
         <v>196298600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>209128800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>195387500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>179979700</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>370400</v>
+        <v>386700</v>
       </c>
       <c r="E47" s="3">
+        <v>373200</v>
+      </c>
+      <c r="F47" s="3">
         <v>301000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>292500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>284700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>295600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>279400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>327200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>384400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E48" s="3">
         <v>169500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>172000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>170600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>176200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>188000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>175000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>181900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>180600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6311400</v>
+        <v>6589400</v>
       </c>
       <c r="E49" s="3">
+        <v>6311500</v>
+      </c>
+      <c r="F49" s="3">
         <v>6790400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6540800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6548500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6751600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6481600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6668300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6671000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6632300</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1931,8 +2044,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1963,40 +2079,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="E52" s="3">
+        <v>800</v>
+      </c>
+      <c r="F52" s="3">
         <v>5200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2027,40 +2149,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>216780800</v>
+        <v>378972900</v>
       </c>
       <c r="E54" s="3">
+        <v>288955200</v>
+      </c>
+      <c r="F54" s="3">
         <v>287703500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>231372700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>238204400</v>
       </c>
-      <c r="H54" s="3">
-        <v>212487400</v>
-      </c>
       <c r="I54" s="3">
+        <v>209469500</v>
+      </c>
+      <c r="J54" s="3">
         <v>203275300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>216338800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>202661200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>187172500</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2073,8 +2201,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2087,200 +2216,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>480700</v>
+        <v>569100</v>
       </c>
       <c r="E57" s="3">
+        <v>232500</v>
+      </c>
+      <c r="F57" s="3">
         <v>494600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>310900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>396200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>165200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>366300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>415400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>548800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>173600</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>590000</v>
+      </c>
+      <c r="E58" s="3">
         <v>551100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>586900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>556100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>51100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>43600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>34200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>29500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>56000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>207911600</v>
+        <v>369622700</v>
       </c>
       <c r="E59" s="3">
+        <v>280087400</v>
+      </c>
+      <c r="F59" s="3">
         <v>278347100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>222721600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>229240000</v>
       </c>
-      <c r="H59" s="3">
-        <v>203391900</v>
-      </c>
       <c r="I59" s="3">
+        <v>200374000</v>
+      </c>
+      <c r="J59" s="3">
         <v>194637600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>207548400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>193600000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>178437800</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>208943400</v>
+        <v>370781800</v>
       </c>
       <c r="E60" s="3">
+        <v>281117800</v>
+      </c>
+      <c r="F60" s="3">
         <v>279428600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>223588600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>229687300</v>
       </c>
-      <c r="H60" s="3">
-        <v>203892000</v>
-      </c>
       <c r="I60" s="3">
+        <v>200874200</v>
+      </c>
+      <c r="J60" s="3">
         <v>195038100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>207993300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>194204700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>178909000</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2674400</v>
+        <v>2820100</v>
       </c>
       <c r="E61" s="3">
+        <v>2674500</v>
+      </c>
+      <c r="F61" s="3">
         <v>2870400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2758800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3312500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3392200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3249200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3353100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3330400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3258300</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11200</v>
+        <v>11500</v>
       </c>
       <c r="E62" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F62" s="3">
         <v>9800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2311,8 +2459,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2343,8 +2494,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2375,40 +2529,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>212223400</v>
+        <v>374231900</v>
       </c>
       <c r="E66" s="3">
+        <v>284397800</v>
+      </c>
+      <c r="F66" s="3">
         <v>282963300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>226984600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>233660400</v>
       </c>
-      <c r="H66" s="3">
-        <v>207971700</v>
-      </c>
       <c r="I66" s="3">
+        <v>204953900</v>
+      </c>
+      <c r="J66" s="3">
         <v>198946500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>212026400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>198213600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>182854500</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2421,8 +2581,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2453,8 +2614,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2485,8 +2649,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2517,8 +2684,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2549,40 +2719,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="E72" s="3">
+        <v>1904900</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3">
         <v>1642600</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
         <v>1706000</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>1355500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>1352700</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2613,8 +2789,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2645,8 +2824,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2677,40 +2859,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4395100</v>
+        <v>4566100</v>
       </c>
       <c r="E76" s="3">
+        <v>4395000</v>
+      </c>
+      <c r="F76" s="3">
         <v>4574500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4244300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4384600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4361300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4186200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4172000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4305600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4182900</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2741,45 +2929,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2810,8 +3004,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2824,40 +3021,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E83" s="3">
         <v>-12900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>44300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>41200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>44000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-9100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>38000</v>
       </c>
       <c r="J83" s="3">
         <v>38000</v>
       </c>
       <c r="K83" s="3">
+        <v>38000</v>
+      </c>
+      <c r="L83" s="3">
         <v>44700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2888,8 +3089,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2920,8 +3124,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2952,8 +3159,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2984,8 +3194,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3016,40 +3229,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>181200</v>
+        <v>206000</v>
       </c>
       <c r="E89" s="3">
+        <v>181300</v>
+      </c>
+      <c r="F89" s="3">
         <v>264800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>119500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>199200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>214900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>184700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>151700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>345700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-157200</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3062,40 +3281,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-7700</v>
+        <v>-7300</v>
       </c>
       <c r="E91" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-6400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5300</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3">
         <v>-13300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3126,8 +3349,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3158,40 +3384,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>36000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-32100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9600</v>
       </c>
-      <c r="H94" s="3">
-        <v>71500</v>
-      </c>
       <c r="I94" s="3">
+        <v>74200</v>
+      </c>
+      <c r="J94" s="3">
         <v>36200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>24000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>37600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-63900</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3204,40 +3436,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>275700</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>258900</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3268,8 +3504,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3300,8 +3539,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3332,100 +3574,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-227800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-108200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-342400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8800</v>
       </c>
-      <c r="H100" s="3">
-        <v>-162000</v>
-      </c>
       <c r="I100" s="3">
+        <v>-164800</v>
+      </c>
+      <c r="J100" s="3">
         <v>-79900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-320700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-15400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-16300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-23000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>44600</v>
+        <v>-33700</v>
       </c>
       <c r="E102" s="3">
+        <v>44800</v>
+      </c>
+      <c r="F102" s="3">
         <v>283500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-250200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>173400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>124100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>148900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-152800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>363600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-228600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
   <si>
     <t>ERNXY</t>
   </si>
@@ -656,62 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +754,11 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -780,8 +792,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -815,8 +830,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -830,8 +848,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,8 +884,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -900,8 +922,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -935,8 +960,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -970,8 +998,11 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -982,8 +1013,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1017,8 +1049,11 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1052,8 +1087,11 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1067,8 +1105,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1102,8 +1141,11 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1137,8 +1179,11 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1172,8 +1217,11 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1207,8 +1255,11 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1242,8 +1293,11 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1277,8 +1331,11 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1312,8 +1369,11 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1347,8 +1407,11 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1382,8 +1445,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1417,8 +1483,11 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1452,8 +1521,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1487,8 +1559,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1522,8 +1597,11 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1557,8 +1635,11 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1592,8 +1673,11 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1627,48 +1711,54 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1682,8 +1772,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1697,113 +1788,123 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1775100</v>
-      </c>
-      <c r="E41" s="3">
+        <v>1079600</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3">
         <v>1732500</v>
       </c>
-      <c r="F41" s="3">
-        <v>1818300</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3">
         <v>1474400</v>
       </c>
-      <c r="H41" s="3">
-        <v>1736500</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>1601400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1414600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1305500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1451200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1069900</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>69700</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>66100</v>
       </c>
-      <c r="F42" s="3">
-        <v>68700</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>94900</v>
       </c>
-      <c r="H42" s="3">
-        <v>113400</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>113900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>180600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>80900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>114300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>173900</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>639500</v>
-      </c>
-      <c r="E43" s="3">
+        <v>525000</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>406300</v>
       </c>
-      <c r="F43" s="3">
-        <v>510600</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>331600</v>
       </c>
-      <c r="H43" s="3">
-        <v>453700</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>352600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>377200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>395400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>505000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>398700</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1837,183 +1938,201 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>369335600</v>
-      </c>
-      <c r="E45" s="3">
+        <v>409751500</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>279831000</v>
       </c>
-      <c r="F45" s="3">
-        <v>277991200</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
         <v>222368700</v>
       </c>
-      <c r="H45" s="3">
-        <v>228851800</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>200097400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>194326200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>207307300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>193317000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>178307700</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>371750200</v>
-      </c>
-      <c r="E46" s="3">
+        <v>411483300</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3">
         <v>282068800</v>
       </c>
-      <c r="F46" s="3">
-        <v>280388800</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3">
         <v>224318400</v>
       </c>
-      <c r="H46" s="3">
-        <v>231155400</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
         <v>202198600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>196298600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>209128800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>195387500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>179979700</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>386700</v>
-      </c>
-      <c r="E47" s="3">
+        <v>477600</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3">
         <v>373200</v>
       </c>
-      <c r="F47" s="3">
-        <v>301000</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3">
         <v>292500</v>
       </c>
-      <c r="H47" s="3">
-        <v>284700</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>295600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>279400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>327200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>384400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>211400</v>
-      </c>
-      <c r="E48" s="3">
+        <v>220900</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3">
         <v>169500</v>
       </c>
-      <c r="F48" s="3">
-        <v>172000</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
         <v>170600</v>
       </c>
-      <c r="H48" s="3">
-        <v>176200</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>188000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>175000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>181900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>180600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6589400</v>
-      </c>
-      <c r="E49" s="3">
+        <v>7735400</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3">
         <v>6311500</v>
       </c>
-      <c r="F49" s="3">
-        <v>6790400</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3">
         <v>6540800</v>
       </c>
-      <c r="H49" s="3">
-        <v>6548500</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3">
         <v>6751600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6481600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6668300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6671000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6632300</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2047,8 +2166,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2082,43 +2204,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3700</v>
-      </c>
-      <c r="E52" s="3">
         <v>800</v>
       </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="F52" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G52" s="3">
+        <v>800</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
         <v>1000</v>
       </c>
-      <c r="H52" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2152,43 +2280,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>378972900</v>
-      </c>
-      <c r="E54" s="3">
+        <v>419946200</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="3">
         <v>288955200</v>
       </c>
-      <c r="F54" s="3">
-        <v>287703500</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3">
         <v>231372700</v>
       </c>
-      <c r="H54" s="3">
-        <v>238204400</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
         <v>209469500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>203275300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>216338800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>202661200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>187172500</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2202,8 +2336,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2217,218 +2352,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>569100</v>
-      </c>
-      <c r="E57" s="3">
+        <v>496200</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3">
         <v>232500</v>
       </c>
-      <c r="F57" s="3">
-        <v>494600</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
         <v>310900</v>
       </c>
-      <c r="H57" s="3">
-        <v>396200</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>165200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>366300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>415400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>548800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>173600</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>590000</v>
-      </c>
-      <c r="E58" s="3">
+        <v>733900</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3">
         <v>551100</v>
       </c>
-      <c r="F58" s="3">
-        <v>586900</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3">
         <v>556100</v>
       </c>
-      <c r="H58" s="3">
-        <v>51100</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3">
         <v>43600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>34200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>29500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>56000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>369622700</v>
-      </c>
-      <c r="E59" s="3">
+        <v>410198300</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>280087400</v>
       </c>
-      <c r="F59" s="3">
-        <v>278347100</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>222721600</v>
       </c>
-      <c r="H59" s="3">
-        <v>229240000</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>200374000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>194637600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>207548400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>193600000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>178437800</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>370781800</v>
-      </c>
-      <c r="E60" s="3">
+        <v>411428400</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3">
         <v>281117800</v>
       </c>
-      <c r="F60" s="3">
-        <v>279428600</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3">
         <v>223588600</v>
       </c>
-      <c r="H60" s="3">
-        <v>229687300</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
         <v>200874200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>195038100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>207993300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>194204700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>178909000</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2820100</v>
+        <v>2796900</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>2674500</v>
       </c>
-      <c r="F61" s="3">
-        <v>2870400</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>2758800</v>
       </c>
-      <c r="H61" s="3">
-        <v>3312500</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>3392200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3249200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3353100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3330400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3258300</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11500</v>
-      </c>
-      <c r="E62" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3">
         <v>10800</v>
       </c>
-      <c r="F62" s="3">
-        <v>9800</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3">
         <v>7600</v>
       </c>
-      <c r="H62" s="3">
-        <v>7800</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>7200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2462,8 +2616,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2497,8 +2654,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2532,43 +2692,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>374231900</v>
-      </c>
-      <c r="E66" s="3">
+        <v>414898800</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3">
         <v>284397800</v>
       </c>
-      <c r="F66" s="3">
-        <v>282963300</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
         <v>226984600</v>
       </c>
-      <c r="H66" s="3">
-        <v>233660400</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
         <v>204953900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>198946500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>212026400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>198213600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>182854500</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2582,8 +2748,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2617,8 +2784,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2652,8 +2822,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2687,8 +2860,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2722,43 +2898,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>2214700</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>1904900</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>1642600</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>1706000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>1355500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>1352700</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2792,8 +2974,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2827,8 +3012,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2862,43 +3050,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4566100</v>
-      </c>
-      <c r="E76" s="3">
+        <v>4877900</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="3">
         <v>4395000</v>
       </c>
-      <c r="F76" s="3">
-        <v>4574500</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3">
         <v>4244300</v>
       </c>
-      <c r="H76" s="3">
-        <v>4384600</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3">
         <v>4361300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4186200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4172000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4305600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4182900</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2932,48 +3126,54 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3007,8 +3207,11 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3022,43 +3225,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>47500</v>
-      </c>
-      <c r="E83" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>-12900</v>
       </c>
-      <c r="F83" s="3">
-        <v>44300</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3">
         <v>41200</v>
       </c>
-      <c r="H83" s="3">
-        <v>44000</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>-9100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>38000</v>
       </c>
       <c r="K83" s="3">
         <v>38000</v>
       </c>
       <c r="L83" s="3">
+        <v>38000</v>
+      </c>
+      <c r="M83" s="3">
         <v>44700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3092,8 +3299,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3127,8 +3337,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3162,8 +3375,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3197,8 +3413,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3232,43 +3451,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>206000</v>
-      </c>
-      <c r="E89" s="3">
+        <v>158500</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3">
         <v>181300</v>
       </c>
-      <c r="F89" s="3">
-        <v>264800</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3">
         <v>119500</v>
       </c>
-      <c r="H89" s="3">
-        <v>199200</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
         <v>214900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>184700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>151700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>345700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-157200</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3282,43 +3507,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="E91" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3">
         <v>-7600</v>
       </c>
-      <c r="F91" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3">
         <v>-5300</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3">
         <v>-13300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3352,8 +3581,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3387,43 +3619,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-15800</v>
-      </c>
-      <c r="E94" s="3">
+        <v>-502800</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
         <v>-31600</v>
       </c>
-      <c r="F94" s="3">
-        <v>36000</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
         <v>-32100</v>
       </c>
-      <c r="H94" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3">
         <v>74200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>36200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>24000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>37600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-63900</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3437,43 +3675,47 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="D96" s="3">
+        <v>344500</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
         <v>275700</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>258900</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3507,8 +3749,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3542,8 +3787,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3577,109 +3825,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-227800</v>
-      </c>
-      <c r="E100" s="3">
+        <v>-499000</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3">
         <v>-108200</v>
       </c>
-      <c r="F100" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3">
         <v>-342400</v>
       </c>
-      <c r="H100" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3">
         <v>-164800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-79900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-320700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="E101" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3">
         <v>-7800</v>
       </c>
-      <c r="H101" s="3">
-        <v>-15400</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3">
         <v>8700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-16300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-23000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>11800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-33700</v>
+        <v>-849000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>44800</v>
       </c>
-      <c r="F102" s="3">
-        <v>283500</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-250200</v>
       </c>
-      <c r="H102" s="3">
-        <v>173400</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>124100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>148900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-152800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>363600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-228600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
@@ -3508,7 +3508,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-36300</v>
+        <v>-3800</v>
       </c>
       <c r="E91" s="3">
         <v>-7600</v>

--- a/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ERNXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>ERNXY</t>
   </si>
@@ -656,65 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,8 +754,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -789,8 +795,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -827,8 +836,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -843,8 +855,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -881,8 +894,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -919,8 +935,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -957,8 +976,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -995,8 +1017,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1008,8 +1033,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1046,8 +1072,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1084,8 +1113,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1100,8 +1132,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1138,8 +1171,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1176,8 +1212,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1214,8 +1253,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1252,8 +1294,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1290,8 +1335,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1328,8 +1376,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1366,8 +1417,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1404,8 +1458,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1442,8 +1499,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1480,8 +1540,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1518,8 +1581,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1556,8 +1622,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1594,8 +1663,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1632,8 +1704,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1670,8 +1745,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1708,51 +1786,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1767,8 +1851,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1783,122 +1868,132 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1871200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1079600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1732500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1474400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1601400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1305500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1069900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>989600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1414600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1305500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1451200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1069900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E42" s="3">
         <v>69700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>66100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>94900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>113900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>80900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>173900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>149000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>180600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>80900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>114300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>173900</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>489100</v>
+      </c>
+      <c r="E43" s="3">
         <v>525000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>406300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>331600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>352600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>395400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>398700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>585800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>377200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>395400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>505000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>398700</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1935,198 +2030,216 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>373445600</v>
+      </c>
+      <c r="E45" s="3">
         <v>409751500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>279831000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>222368700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200097400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>207307300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>178307700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>176320100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>194326200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>207307300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>193317000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>178307700</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>375920400</v>
+      </c>
+      <c r="E46" s="3">
         <v>411483300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>282068800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>224318400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>202198600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>209128800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>179979700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>178085200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>196298600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>209128800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>195387500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>179979700</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>519600</v>
+      </c>
+      <c r="E47" s="3">
         <v>477600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>373200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>292500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>295600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>327200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>376800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>383300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>279400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>327200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>384400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>237300</v>
+      </c>
+      <c r="E48" s="3">
         <v>220900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>169500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>170600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>188000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>181900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>162100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>164100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>175000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>181900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>180600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7956900</v>
+      </c>
+      <c r="E49" s="3">
         <v>7735400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6311500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6540800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6751600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6668300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6632300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6423900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6481600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6668300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6671000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6632300</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2163,8 +2276,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2201,46 +2317,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>800</v>
+        <v>13600</v>
       </c>
       <c r="E52" s="3">
         <v>800</v>
       </c>
       <c r="F52" s="3">
+        <v>800</v>
+      </c>
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2277,46 +2399,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>384678000</v>
+      </c>
+      <c r="E54" s="3">
         <v>419946200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>288955200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>231372700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>209469500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>216338800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>187172500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>185109700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>203275300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>216338800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>202661200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>187172500</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2331,8 +2459,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2347,198 +2476,214 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>255300</v>
+      </c>
+      <c r="E57" s="3">
         <v>496200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>232500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>310900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>165200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>415400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>173600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>705700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>366300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>415400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>548800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>173600</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>494600</v>
+      </c>
+      <c r="E58" s="3">
         <v>733900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>551100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>556100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>43600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>29500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>49000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>29200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>34200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>29500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>56000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>373798600</v>
+      </c>
+      <c r="E59" s="3">
         <v>410198300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>280087400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>222721600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>200374000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>207548400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>178437800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>176512800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>194637600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>207548400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>193600000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>178437800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>374903500</v>
+      </c>
+      <c r="E60" s="3">
         <v>411428400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>281117800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>223588600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>200874200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>207993300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>178909000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>177247700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>195038100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>207993300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>194204700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>178909000</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3498800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2796900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2674500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2758800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3392200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3353100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3258300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3197100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3249200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3353100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3330400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3258300</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2546,37 +2691,40 @@
         <v>12400</v>
       </c>
       <c r="E62" s="3">
-        <v>10800</v>
+        <v>12400</v>
       </c>
       <c r="F62" s="3">
+        <v>11000</v>
+      </c>
+      <c r="G62" s="3">
         <v>7600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2613,8 +2761,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2651,8 +2802,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2689,46 +2843,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>379118600</v>
+      </c>
+      <c r="E66" s="3">
         <v>414898800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>284397800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>226984600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>204953900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>212026400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>182854500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>181157600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>198946500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>212026400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>198213600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>182854500</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2743,8 +2903,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2781,8 +2942,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2819,8 +2983,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2857,8 +3024,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2895,46 +3065,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2569700</v>
+      </c>
+      <c r="E72" s="3">
         <v>2214700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1904900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1642600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1706000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1355500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1352700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1132300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>1355500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>1352700</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2971,8 +3147,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3009,8 +3188,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3047,46 +3229,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5327900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4877900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4395000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4244300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4361300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4172000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4182900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3865400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4186200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4172000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4305600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4182900</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3123,51 +3311,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3204,8 +3398,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3220,46 +3417,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E83" s="3">
         <v>41200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-9100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>38000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>29000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>38000</v>
       </c>
       <c r="L83" s="3">
         <v>38000</v>
       </c>
       <c r="M83" s="3">
+        <v>38000</v>
+      </c>
+      <c r="N83" s="3">
         <v>44700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3296,8 +3497,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3334,8 +3538,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3372,8 +3579,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3410,8 +3620,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3448,46 +3661,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E89" s="3">
         <v>158500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>181300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>119500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>214900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>151700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-157200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>80300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>184700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>151700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>345700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-157200</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3502,46 +3721,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3578,8 +3801,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3616,46 +3842,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>104600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-502800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-32100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>74200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>24000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-63900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>36200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>24000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>37600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-63900</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3670,46 +3902,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>344500</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>275700</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>258900</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>215300</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
         <v>258900</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3746,8 +3982,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3784,8 +4023,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3822,118 +4064,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>212700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-499000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-108200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-342400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-164800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-320700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-16300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-268700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-79900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-320700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-23000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>9800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-16300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-23000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>11800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>409400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-849000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>44800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-250200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>124100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-152800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-228600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-217500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>148900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-152800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>363600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-228600</v>
       </c>
     </row>
